--- a/database/watch/Videos.xlsx
+++ b/database/watch/Videos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Cursor AI\database\watch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6D0FEFB-C62A-479A-A210-CD2A0CB9F314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05D32234-ED7C-4E97-8851-D02D7E42B654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2985" yWindow="2985" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,9 +42,6 @@
     <t>Message From The Past</t>
   </si>
   <si>
-    <t>A2-B1</t>
-  </si>
-  <si>
     <t>Late at night, your phone vibrates.
 A message appears from someone you haven’t talked to in a long time… someone special.
 What will you do? And what does the next message say?</t>
@@ -66,6 +63,9 @@
   </si>
   <si>
     <t xml:space="preserve">https://youtu.be/87pZ_djGyv8 </t>
+  </si>
+  <si>
+    <t>A2-B1 (Lower Inter)</t>
   </si>
 </sst>
 </file>
@@ -421,7 +421,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -444,13 +444,13 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -458,16 +458,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="E3" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
